--- a/src/main/resources/MEDIATION_CONTRACT_BALANCES_TEMPLATE.xlsx
+++ b/src/main/resources/MEDIATION_CONTRACT_BALANCES_TEMPLATE.xlsx
@@ -7,8 +7,6 @@
   </bookViews>
   <sheets>
     <sheet name="MAIN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="DATA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Adjusted Expenditure" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'MAIN'!$C$5:$E$7</definedName>
@@ -1089,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
@@ -1544,161 +1542,4 @@
   <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.1574803149606299" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="portrait" paperSize="9" scale="92"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr codeName="Sheet2">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13.140625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="12.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="13.28515625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="14.42578125" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="12.5703125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="13.5703125" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="14.7109375" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="23.85546875" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="25" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="20" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="16.42578125" bestFit="1" customWidth="1" min="11" max="11"/>
-    <col width="19.7109375" bestFit="1" customWidth="1" min="12" max="12"/>
-    <col width="28.42578125" bestFit="1" customWidth="1" min="13" max="13"/>
-    <col width="26.42578125" bestFit="1" customWidth="1" min="14" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="1" s="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>OFFICE_CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>OLD_CLAIMS</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>NEW_CLAIMS</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL_CLAIMS</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>OLD_EXPEND</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>NEW_EXPEND</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL_EXPEND</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>BAL_OF_CLAIMS_N_PAYS</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>CONTRACT_ADJUSTMENTS</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>CONTRACT_BALANCE</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>IN_YEAR_CLAIMS</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>IN_YEAR_PAYMENTS</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>PAYMENT_RUN_ADJUSTMENT</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>FINAL_CONTRACT_BALANCE</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr codeName="Sheet3">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18.140625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="14.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="43.7109375" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="10.140625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="19.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="11.85546875" bestFit="1" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="1" s="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PARTY_SITE_NAME</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>PARTY_SITE_ID</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>INVOICE_NUM</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PAY_DATE</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>SUB_SCHEME</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>PAID_TOTAL</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>